--- a/salidas/empresas/GD.xlsx
+++ b/salidas/empresas/GD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>36.96715927124023</v>
+        <v>36.96716690063477</v>
       </c>
       <c r="C2" t="n">
         <v>58.18000030517578</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>39.16243362426758</v>
+        <v>39.16244506835938</v>
       </c>
       <c r="C3" t="n">
         <v>61.6349983215332</v>
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>40.57981109619141</v>
+        <v>40.57979583740234</v>
       </c>
       <c r="C6" t="n">
         <v>63.63999938964844</v>
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>42.88632583618164</v>
+        <v>42.88631820678711</v>
       </c>
       <c r="C8" t="n">
         <v>67.01999664306641</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>43.22546768188477</v>
+        <v>43.22548294067383</v>
       </c>
       <c r="C9" t="n">
         <v>67.55000305175781</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>45.63869857788086</v>
+        <v>45.63871383666992</v>
       </c>
       <c r="C11" t="n">
         <v>71.09999847412109</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>47.72486114501953</v>
+        <v>47.72485733032227</v>
       </c>
       <c r="C13" t="n">
         <v>74.34999847412109</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>50.30931854248047</v>
+        <v>50.30933380126953</v>
       </c>
       <c r="C14" t="n">
         <v>78.15000152587891</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>49.16986846923828</v>
+        <v>49.16989517211914</v>
       </c>
       <c r="C15" t="n">
         <v>76.37999725341797</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>49.1827392578125</v>
+        <v>49.18274688720703</v>
       </c>
       <c r="C16" t="n">
         <v>76.40000152587891</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>50.72228240966797</v>
+        <v>50.72227478027344</v>
       </c>
       <c r="C17" t="n">
         <v>78.5</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>51.84658050537109</v>
+        <v>51.84657669067383</v>
       </c>
       <c r="C18" t="n">
         <v>80.23999786376953</v>
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>50.95003890991211</v>
+        <v>50.95001602172852</v>
       </c>
       <c r="C20" t="n">
         <v>78.55999755859375</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>50.95003890991211</v>
+        <v>50.95001602172852</v>
       </c>
       <c r="C21" t="n">
         <v>78.55999755859375</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>54.78296661376953</v>
+        <v>54.78295135498047</v>
       </c>
       <c r="C22" t="n">
         <v>84.47000122070312</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>59.19800567626953</v>
+        <v>59.19800186157227</v>
       </c>
       <c r="C23" t="n">
         <v>90.95999908447266</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>57.91587829589844</v>
+        <v>57.91587066650391</v>
       </c>
       <c r="C25" t="n">
         <v>88.98999786376953</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>55.20092010498047</v>
+        <v>55.20091247558594</v>
       </c>
       <c r="C26" t="n">
         <v>84.52999877929688</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>54.44338607788086</v>
+        <v>54.44336700439453</v>
       </c>
       <c r="C28" t="n">
         <v>83.37000274658203</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>59.29195404052734</v>
+        <v>59.29198455810547</v>
       </c>
       <c r="C29" t="n">
         <v>90.41999816894531</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>60.42640686035156</v>
+        <v>60.42642593383789</v>
       </c>
       <c r="C30" t="n">
         <v>92.15000152587891</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>55.21329116821289</v>
+        <v>55.21327209472656</v>
       </c>
       <c r="C31" t="n">
         <v>84.19999694824219</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>58.69661331176758</v>
+        <v>58.69663619995117</v>
       </c>
       <c r="C32" t="n">
         <v>89.13999938964844</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>60.77741622924805</v>
+        <v>60.77743911743164</v>
       </c>
       <c r="C33" t="n">
         <v>92.30000305175781</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>48.47709655761719</v>
+        <v>48.47705459594727</v>
       </c>
       <c r="C34" t="n">
         <v>73.62000274658203</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>39.93418121337891</v>
+        <v>39.93417739868164</v>
       </c>
       <c r="C35" t="n">
         <v>60.31999969482422</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>34.20754623413086</v>
+        <v>34.20753860473633</v>
       </c>
       <c r="C36" t="n">
         <v>51.66999816894531</v>
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>37.79755020141602</v>
+        <v>37.79756164550781</v>
       </c>
       <c r="C38" t="n">
         <v>56.72999954223633</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>29.19599723815918</v>
+        <v>29.19600486755371</v>
       </c>
       <c r="C39" t="n">
         <v>43.81999969482422</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>27.71021461486816</v>
+        <v>27.7102165222168</v>
       </c>
       <c r="C40" t="n">
         <v>41.59000015258789</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>34.71576309204102</v>
+        <v>34.71577835083008</v>
       </c>
       <c r="C41" t="n">
         <v>51.66999816894531</v>
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>37.46491622924805</v>
+        <v>37.46490478515625</v>
       </c>
       <c r="C43" t="n">
         <v>55.38999938964844</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>37.46491622924805</v>
+        <v>37.46490478515625</v>
       </c>
       <c r="C44" t="n">
         <v>55.38999938964844</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>40.03519439697266</v>
+        <v>40.03516387939453</v>
       </c>
       <c r="C45" t="n">
         <v>59.18999862670898</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>43.69441223144531</v>
+        <v>43.69441986083984</v>
       </c>
       <c r="C46" t="n">
         <v>64.59999847412109</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>42.65517044067383</v>
+        <v>42.65517807006836</v>
       </c>
       <c r="C47" t="n">
         <v>62.70000076293945</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>44.83214569091797</v>
+        <v>44.8321533203125</v>
       </c>
       <c r="C48" t="n">
         <v>65.90000152587891</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>46.37642669677734</v>
+        <v>46.37643432617188</v>
       </c>
       <c r="C49" t="n">
         <v>68.16999816894531</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>45.72560882568359</v>
+        <v>45.72560501098633</v>
       </c>
       <c r="C50" t="n">
         <v>66.84999847412109</v>
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>52.8050422668457</v>
+        <v>52.80503845214844</v>
       </c>
       <c r="C52" t="n">
         <v>77.19999694824219</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>52.51540374755859</v>
+        <v>52.51539611816406</v>
       </c>
       <c r="C53" t="n">
         <v>76.36000061035156</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>46.69718551635742</v>
+        <v>46.69716644287109</v>
       </c>
       <c r="C54" t="n">
         <v>67.90000152587891</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>40.56038665771484</v>
+        <v>40.56037139892578</v>
       </c>
       <c r="C55" t="n">
         <v>58.56000137329102</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>42.42356872558594</v>
+        <v>42.42355728149414</v>
       </c>
       <c r="C56" t="n">
         <v>61.25</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>38.69720077514648</v>
+        <v>38.69720458984375</v>
       </c>
       <c r="C57" t="n">
         <v>55.86999893188477</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>43.50405120849609</v>
+        <v>43.50406265258789</v>
       </c>
       <c r="C58" t="n">
         <v>62.81000137329102</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>47.49653625488281</v>
+        <v>47.49652099609375</v>
       </c>
       <c r="C59" t="n">
         <v>68.12000274658203</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>46.08110809326172</v>
+        <v>46.08108901977539</v>
       </c>
       <c r="C60" t="n">
         <v>66.08999633789062</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>49.47668075561523</v>
+        <v>49.47669982910156</v>
       </c>
       <c r="C61" t="n">
         <v>70.95999908447266</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>52.88421249389648</v>
+        <v>52.88420486450195</v>
       </c>
       <c r="C62" t="n">
         <v>75.40000152587891</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>53.38920211791992</v>
+        <v>53.38920974731445</v>
       </c>
       <c r="C63" t="n">
         <v>76.12000274658203</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>53.69781112670898</v>
+        <v>53.69783020019531</v>
       </c>
       <c r="C64" t="n">
         <v>76.55999755859375</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>51.39847946166992</v>
+        <v>51.39845657348633</v>
       </c>
       <c r="C65" t="n">
         <v>72.81999969482422</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>52.38662719726562</v>
+        <v>52.38664627075195</v>
       </c>
       <c r="C66" t="n">
         <v>74.22000122070312</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>52.9357795715332</v>
+        <v>52.93579483032227</v>
       </c>
       <c r="C67" t="n">
         <v>74.51999664306641</v>
@@ -1894,7 +1906,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>45.51966857910156</v>
+        <v>45.51966094970703</v>
       </c>
       <c r="C69" t="n">
         <v>64.08000183105469</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>40.41220855712891</v>
+        <v>40.41219329833984</v>
       </c>
       <c r="C70" t="n">
         <v>56.88999938964844</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>45.97615814208984</v>
+        <v>45.97616958618164</v>
       </c>
       <c r="C71" t="n">
         <v>64.19000244140625</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>47.31555938720703</v>
+        <v>47.3155632019043</v>
       </c>
       <c r="C72" t="n">
         <v>66.05999755859375</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>47.56625747680664</v>
+        <v>47.56624984741211</v>
       </c>
       <c r="C73" t="n">
         <v>66.41000366210938</v>
@@ -2068,7 +2080,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>52.79839324951172</v>
+        <v>52.79839706420898</v>
       </c>
       <c r="C75" t="n">
         <v>73.23000335693359</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>52.90653991699219</v>
+        <v>52.90653228759766</v>
       </c>
       <c r="C76" t="n">
         <v>73.37999725341797</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>49.02696990966797</v>
+        <v>49.0269660949707</v>
       </c>
       <c r="C77" t="n">
         <v>67.5</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>46.49208831787109</v>
+        <v>46.49209594726562</v>
       </c>
       <c r="C78" t="n">
         <v>64.01000213623047</v>
@@ -2213,7 +2225,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>46.43656921386719</v>
+        <v>46.43658447265625</v>
       </c>
       <c r="C80" t="n">
         <v>63.43999862670898</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>47.95177459716797</v>
+        <v>47.9517822265625</v>
       </c>
       <c r="C81" t="n">
         <v>65.51000213623047</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>48.39828872680664</v>
+        <v>48.39828491210938</v>
       </c>
       <c r="C82" t="n">
         <v>66.12000274658203</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>50.21347808837891</v>
+        <v>50.21345138549805</v>
       </c>
       <c r="C83" t="n">
         <v>68.08000183105469</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>49.04812622070312</v>
+        <v>49.04811477661133</v>
       </c>
       <c r="C84" t="n">
         <v>66.5</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>51.47726058959961</v>
+        <v>51.47725296020508</v>
       </c>
       <c r="C85" t="n">
         <v>69.26999664306641</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>49.2701301574707</v>
+        <v>49.27013397216797</v>
       </c>
       <c r="C86" t="n">
         <v>66.30000305175781</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>50.51117706298828</v>
+        <v>50.51115798950195</v>
       </c>
       <c r="C87" t="n">
         <v>67.97000122070312</v>
@@ -2472,11 +2484,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>52.39875411987305</v>
+        <v>52.39875030517578</v>
       </c>
       <c r="C88" t="n">
         <v>70.51000213623047</v>
@@ -2499,11 +2511,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>55.4101448059082</v>
+        <v>55.41012191772461</v>
       </c>
       <c r="C89" t="n">
         <v>73.95999908447266</v>
@@ -2526,11 +2538,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>57.76259231567383</v>
+        <v>57.76260757446289</v>
       </c>
       <c r="C90" t="n">
         <v>77.09999847412109</v>
@@ -2553,11 +2565,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>58.68410873413086</v>
+        <v>58.68410491943359</v>
       </c>
       <c r="C91" t="n">
         <v>78.33000183105469</v>
@@ -2580,11 +2592,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>64.39231872558594</v>
+        <v>64.39230346679688</v>
       </c>
       <c r="C92" t="n">
         <v>85.33999633789062</v>
@@ -2607,11 +2619,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>62.81534194946289</v>
+        <v>62.81532669067383</v>
       </c>
       <c r="C93" t="n">
         <v>83.25</v>
@@ -2634,7 +2646,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2661,11 +2673,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>65.79933166503906</v>
+        <v>65.79932403564453</v>
       </c>
       <c r="C95" t="n">
         <v>86.62999725341797</v>
@@ -2688,7 +2700,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2715,11 +2727,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>72.574462890625</v>
+        <v>72.57447052001953</v>
       </c>
       <c r="C97" t="n">
         <v>95.55000305175781</v>
@@ -2742,11 +2754,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>77.40115356445312</v>
+        <v>77.40113830566406</v>
       </c>
       <c r="C98" t="n">
         <v>101.3099975585938</v>
@@ -2769,11 +2781,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>83.68889617919922</v>
+        <v>83.68886566162109</v>
       </c>
       <c r="C99" t="n">
         <v>109.5400009155273</v>
@@ -2798,11 +2810,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>83.21520233154297</v>
+        <v>83.21519470214844</v>
       </c>
       <c r="C100" t="n">
         <v>108.9199981689453</v>
@@ -2827,11 +2839,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>84.11032104492188</v>
+        <v>84.11033630371094</v>
       </c>
       <c r="C101" t="n">
         <v>109.4499969482422</v>
@@ -2856,11 +2868,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>90.7730712890625</v>
+        <v>90.77308654785156</v>
       </c>
       <c r="C102" t="n">
         <v>118.120002746582</v>
@@ -2885,7 +2897,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2914,11 +2926,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>90.21552276611328</v>
+        <v>90.21551513671875</v>
       </c>
       <c r="C104" t="n">
         <v>116.7699966430664</v>
@@ -2943,11 +2955,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>95.22193908691406</v>
+        <v>95.22193145751953</v>
       </c>
       <c r="C105" t="n">
         <v>123.25</v>
@@ -2972,11 +2984,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>98.18865966796875</v>
+        <v>98.18868255615234</v>
       </c>
       <c r="C106" t="n">
         <v>127.0899963378906</v>
@@ -3001,11 +3013,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>108.5349884033203</v>
+        <v>108.5349655151367</v>
       </c>
       <c r="C107" t="n">
         <v>139.7599945068359</v>
@@ -3030,11 +3042,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>112.8838500976562</v>
+        <v>112.8838119506836</v>
       </c>
       <c r="C108" t="n">
         <v>145.3600006103516</v>
@@ -3059,7 +3071,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3088,11 +3100,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>103.9159622192383</v>
+        <v>103.9159698486328</v>
       </c>
       <c r="C110" t="n">
         <v>133.2100067138672</v>
@@ -3117,7 +3129,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3146,11 +3158,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>105.8817977905273</v>
+        <v>105.8817672729492</v>
       </c>
       <c r="C112" t="n">
         <v>135.7299957275391</v>
@@ -3175,11 +3187,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>107.6724243164062</v>
+        <v>107.6724624633789</v>
       </c>
       <c r="C113" t="n">
         <v>137.3200073242188</v>
@@ -3204,11 +3216,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>109.8993148803711</v>
+        <v>109.899284362793</v>
       </c>
       <c r="C114" t="n">
         <v>140.1600036621094</v>
@@ -3233,11 +3245,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>111.6420669555664</v>
+        <v>111.6420593261719</v>
       </c>
       <c r="C115" t="n">
         <v>141.6900024414062</v>
@@ -3262,11 +3274,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>117.4885025024414</v>
+        <v>117.4885101318359</v>
       </c>
       <c r="C116" t="n">
         <v>149.1100006103516</v>
@@ -3291,11 +3303,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>111.9099960327148</v>
+        <v>111.9099426269531</v>
       </c>
       <c r="C117" t="n">
         <v>142.0299987792969</v>
@@ -3320,11 +3332,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>108.6951751708984</v>
+        <v>108.695182800293</v>
       </c>
       <c r="C118" t="n">
         <v>137.9499969482422</v>
@@ -3349,11 +3361,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>117.6480102539062</v>
+        <v>117.6480255126953</v>
       </c>
       <c r="C119" t="n">
         <v>148.5800018310547</v>
@@ -3378,7 +3390,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3407,11 +3419,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>108.7638320922852</v>
+        <v>108.7638549804688</v>
       </c>
       <c r="C121" t="n">
         <v>137.3600006103516</v>
@@ -3436,11 +3448,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>106.4757308959961</v>
+        <v>106.4757537841797</v>
       </c>
       <c r="C122" t="n">
         <v>133.7700042724609</v>
@@ -3465,11 +3477,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>108.4656677246094</v>
+        <v>108.4656600952148</v>
       </c>
       <c r="C123" t="n">
         <v>136.2700042724609</v>
@@ -3494,11 +3506,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>104.5654449462891</v>
+        <v>104.5654602050781</v>
       </c>
       <c r="C124" t="n">
         <v>131.3699951171875</v>
@@ -3523,11 +3535,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>112.5019378662109</v>
+        <v>112.5019912719727</v>
       </c>
       <c r="C125" t="n">
         <v>140.5200042724609</v>
@@ -3552,7 +3564,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3581,11 +3593,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>112.1133728027344</v>
+        <v>112.1133346557617</v>
       </c>
       <c r="C127" t="n">
         <v>139.2400054931641</v>
@@ -3610,11 +3622,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>118.2729873657227</v>
+        <v>118.2730178833008</v>
       </c>
       <c r="C128" t="n">
         <v>146.8899993896484</v>
@@ -3639,11 +3651,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>122.5645370483398</v>
+        <v>122.5645751953125</v>
       </c>
       <c r="C129" t="n">
         <v>152.2200012207031</v>
@@ -3668,11 +3680,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>124.9318008422852</v>
+        <v>124.931770324707</v>
       </c>
       <c r="C130" t="n">
         <v>155.1600036621094</v>
@@ -3697,11 +3709,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>121.9766464233398</v>
+        <v>121.9766616821289</v>
       </c>
       <c r="C131" t="n">
         <v>150.7400054931641</v>
@@ -3726,11 +3738,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>141.8907318115234</v>
+        <v>141.8906707763672</v>
       </c>
       <c r="C132" t="n">
         <v>175.3500061035156</v>
@@ -3755,7 +3767,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3784,11 +3796,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>147.1629180908203</v>
+        <v>147.1629028320312</v>
       </c>
       <c r="C134" t="n">
         <v>181.0800018310547</v>
@@ -3813,11 +3825,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>154.2577362060547</v>
+        <v>154.2577667236328</v>
       </c>
       <c r="C135" t="n">
         <v>189.8099975585938</v>
@@ -3842,11 +3854,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>152.1365661621094</v>
+        <v>152.1365966796875</v>
       </c>
       <c r="C136" t="n">
         <v>187.1999969482422</v>
@@ -3871,11 +3883,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>158.2001953125</v>
+        <v>158.2001495361328</v>
       </c>
       <c r="C137" t="n">
         <v>193.7899932861328</v>
@@ -3900,11 +3912,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>165.9228057861328</v>
+        <v>165.9228210449219</v>
       </c>
       <c r="C138" t="n">
         <v>203.25</v>
@@ -3929,11 +3941,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>161.7186279296875</v>
+        <v>161.7186737060547</v>
       </c>
       <c r="C139" t="n">
         <v>198.1000061035156</v>
@@ -3958,11 +3970,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>160.9508514404297</v>
+        <v>160.9508819580078</v>
       </c>
       <c r="C140" t="n">
         <v>196.3300018310547</v>
@@ -3987,11 +3999,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>165.0662536621094</v>
+        <v>165.0662078857422</v>
       </c>
       <c r="C141" t="n">
         <v>201.3500061035156</v>
@@ -4016,11 +4028,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>168.5339508056641</v>
+        <v>168.5339660644531</v>
       </c>
       <c r="C142" t="n">
         <v>205.5800018310547</v>
@@ -4045,11 +4057,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>167.066650390625</v>
+        <v>167.0666351318359</v>
       </c>
       <c r="C143" t="n">
         <v>202.9799957275391</v>
@@ -4074,11 +4086,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>170.5071105957031</v>
+        <v>170.507080078125</v>
       </c>
       <c r="C144" t="n">
         <v>207.1600036621094</v>
@@ -4103,11 +4115,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>167.4534912109375</v>
+        <v>167.4535369873047</v>
       </c>
       <c r="C145" t="n">
         <v>203.4499969482422</v>
@@ -4132,11 +4144,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>183.8571472167969</v>
+        <v>183.857177734375</v>
       </c>
       <c r="C146" t="n">
         <v>222.4799957275391</v>
@@ -4161,11 +4173,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>183.8323822021484</v>
+        <v>183.8323669433594</v>
       </c>
       <c r="C147" t="n">
         <v>222.4499969482422</v>
@@ -4190,11 +4202,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>182.5514526367188</v>
+        <v>182.5514221191406</v>
       </c>
       <c r="C148" t="n">
         <v>220.8999938964844</v>
@@ -4219,7 +4231,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4248,11 +4260,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>167.4125671386719</v>
+        <v>167.4126281738281</v>
       </c>
       <c r="C150" t="n">
         <v>201.7100067138672</v>
@@ -4277,11 +4289,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>154.7141418457031</v>
+        <v>154.714111328125</v>
       </c>
       <c r="C151" t="n">
         <v>186.4100036621094</v>
@@ -4306,11 +4318,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>166.6110076904297</v>
+        <v>166.6109924316406</v>
       </c>
       <c r="C152" t="n">
         <v>199.7599945068359</v>
@@ -4335,11 +4347,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>161.3064422607422</v>
+        <v>161.3063507080078</v>
       </c>
       <c r="C153" t="n">
         <v>193.3999938964844</v>
@@ -4364,11 +4376,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>170.7479248046875</v>
+        <v>170.7479400634766</v>
       </c>
       <c r="C154" t="n">
         <v>204.7200012207031</v>
@@ -4393,11 +4405,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>144.5950927734375</v>
+        <v>144.5950469970703</v>
       </c>
       <c r="C155" t="n">
         <v>172.5800018310547</v>
@@ -4422,11 +4434,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>154.9088745117188</v>
+        <v>154.9089050292969</v>
       </c>
       <c r="C156" t="n">
         <v>184.8899993896484</v>
@@ -4451,11 +4463,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>131.7173767089844</v>
+        <v>131.7174377441406</v>
       </c>
       <c r="C157" t="n">
         <v>157.2100067138672</v>
@@ -4480,11 +4492,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>144.2335815429688</v>
+        <v>144.2335968017578</v>
       </c>
       <c r="C158" t="n">
         <v>171.1699981689453</v>
@@ -4509,11 +4521,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>143.43310546875</v>
+        <v>143.4331359863281</v>
       </c>
       <c r="C159" t="n">
         <v>170.2200012207031</v>
@@ -4538,11 +4550,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>142.6410369873047</v>
+        <v>142.6410217285156</v>
       </c>
       <c r="C160" t="n">
         <v>169.2799987792969</v>
@@ -4567,7 +4579,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4596,7 +4608,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4625,11 +4637,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>154.1359405517578</v>
+        <v>154.1359100341797</v>
       </c>
       <c r="C163" t="n">
         <v>181.8200073242188</v>
@@ -4654,11 +4666,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>158.5092926025391</v>
+        <v>158.5093688964844</v>
       </c>
       <c r="C164" t="n">
         <v>185.9400024414062</v>
@@ -4683,11 +4695,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>163.0530395507812</v>
+        <v>163.0530548095703</v>
       </c>
       <c r="C165" t="n">
         <v>191.2700042724609</v>
@@ -4712,11 +4724,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>155.7729034423828</v>
+        <v>155.7728881835938</v>
       </c>
       <c r="C166" t="n">
         <v>182.7299957275391</v>
@@ -4741,11 +4753,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>151.5910034179688</v>
+        <v>151.5910491943359</v>
       </c>
       <c r="C167" t="n">
         <v>176.8000030517578</v>
@@ -4770,7 +4782,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4799,11 +4811,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>151.2052001953125</v>
+        <v>151.2052459716797</v>
       </c>
       <c r="C169" t="n">
         <v>176.3500061035156</v>
@@ -4828,11 +4840,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>151.2745819091797</v>
+        <v>151.2745361328125</v>
       </c>
       <c r="C170" t="n">
         <v>175.4400024414062</v>
@@ -4857,7 +4869,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4886,11 +4898,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>114.0853958129883</v>
+        <v>114.0853652954102</v>
       </c>
       <c r="C172" t="n">
         <v>132.3099975585938</v>
@@ -4915,11 +4927,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>113.5575942993164</v>
+        <v>113.5575714111328</v>
       </c>
       <c r="C173" t="n">
         <v>130.6199951171875</v>
@@ -4944,11 +4956,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>127.6501007080078</v>
+        <v>127.6501083374023</v>
       </c>
       <c r="C174" t="n">
         <v>146.8300018310547</v>
@@ -4973,7 +4985,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5002,7 +5014,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5031,11 +5043,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>130.8036651611328</v>
+        <v>130.8036193847656</v>
       </c>
       <c r="C177" t="n">
         <v>149.3500061035156</v>
@@ -5060,11 +5072,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>121.2396774291992</v>
+        <v>121.2397003173828</v>
       </c>
       <c r="C178" t="n">
         <v>138.4299926757812</v>
@@ -5089,11 +5101,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>115.9014282226562</v>
+        <v>115.9014358520508</v>
       </c>
       <c r="C179" t="n">
         <v>131.3300018310547</v>
@@ -5118,11 +5130,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>131.804443359375</v>
+        <v>131.8044281005859</v>
       </c>
       <c r="C180" t="n">
         <v>149.3500061035156</v>
@@ -5147,7 +5159,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5176,11 +5188,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>130.3878021240234</v>
+        <v>130.3877868652344</v>
       </c>
       <c r="C182" t="n">
         <v>146.6799926757812</v>
@@ -5205,11 +5217,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>145.3128967285156</v>
+        <v>145.3128814697266</v>
       </c>
       <c r="C183" t="n">
         <v>163.4700012207031</v>
@@ -5234,11 +5246,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>161.3935852050781</v>
+        <v>161.3935699462891</v>
       </c>
       <c r="C184" t="n">
         <v>181.5599975585938</v>
@@ -5263,11 +5275,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>170.1965789794922</v>
+        <v>170.1965942382812</v>
       </c>
       <c r="C185" t="n">
         <v>190.2299957275391</v>
@@ -5292,11 +5304,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>169.9102935791016</v>
+        <v>169.9102783203125</v>
       </c>
       <c r="C186" t="n">
         <v>189.9100036621094</v>
@@ -5321,11 +5333,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>168.4340209960938</v>
+        <v>168.43408203125</v>
       </c>
       <c r="C187" t="n">
         <v>188.2599945068359</v>
@@ -5350,11 +5362,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>176.5014343261719</v>
+        <v>176.5014953613281</v>
       </c>
       <c r="C188" t="n">
         <v>196.0299987792969</v>
@@ -5379,11 +5391,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>180.3551025390625</v>
+        <v>180.3550720214844</v>
       </c>
       <c r="C189" t="n">
         <v>200.3099975585938</v>
@@ -5408,11 +5420,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>176.5014343261719</v>
+        <v>176.5014953613281</v>
       </c>
       <c r="C190" t="n">
         <v>196.0299987792969</v>
@@ -5437,11 +5449,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>183.648193359375</v>
+        <v>183.6481781005859</v>
       </c>
       <c r="C191" t="n">
         <v>202.75</v>
@@ -5466,11 +5478,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>171.1664886474609</v>
+        <v>171.1665191650391</v>
       </c>
       <c r="C192" t="n">
         <v>188.9700012207031</v>
@@ -5495,11 +5507,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>188.8293151855469</v>
+        <v>188.829345703125</v>
       </c>
       <c r="C193" t="n">
         <v>208.4700012207031</v>
@@ -5524,11 +5536,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>193.2021789550781</v>
+        <v>193.2021942138672</v>
       </c>
       <c r="C194" t="n">
         <v>212.1000061035156</v>
@@ -5553,11 +5565,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>213.5608367919922</v>
+        <v>213.5608062744141</v>
       </c>
       <c r="C195" t="n">
         <v>234.4499969482422</v>
@@ -5582,7 +5594,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5611,11 +5623,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>216.5890045166016</v>
+        <v>216.5890197753906</v>
       </c>
       <c r="C197" t="n">
         <v>236.5299987792969</v>
@@ -5640,7 +5652,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5669,7 +5681,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5698,7 +5710,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5727,11 +5739,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>210.8412475585938</v>
+        <v>210.8412628173828</v>
       </c>
       <c r="C201" t="n">
         <v>228.9299926757812</v>
@@ -5756,11 +5768,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>195.4055023193359</v>
+        <v>195.4055480957031</v>
       </c>
       <c r="C202" t="n">
         <v>212.1699981689453</v>
@@ -5785,7 +5797,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5814,11 +5826,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>233.746826171875</v>
+        <v>233.7468566894531</v>
       </c>
       <c r="C204" t="n">
         <v>252.3899993896484</v>
@@ -5843,11 +5855,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>229.7829895019531</v>
+        <v>229.7829742431641</v>
       </c>
       <c r="C205" t="n">
         <v>248.1100006103516</v>
@@ -5872,11 +5884,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>216.9983367919922</v>
+        <v>216.9983520507812</v>
       </c>
       <c r="C206" t="n">
         <v>233.0599975585938</v>
@@ -5901,11 +5913,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>212.2032623291016</v>
+        <v>212.2032775878906</v>
       </c>
       <c r="C207" t="n">
         <v>227.9100036621094</v>
@@ -5930,11 +5942,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>212.4825897216797</v>
+        <v>212.4826202392578</v>
       </c>
       <c r="C208" t="n">
         <v>228.2100067138672</v>
@@ -5959,7 +5971,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5988,7 +6000,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6017,7 +6029,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6046,11 +6058,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>210.6695556640625</v>
+        <v>210.6695404052734</v>
       </c>
       <c r="C212" t="n">
         <v>223.5800018310547</v>
@@ -6075,7 +6087,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6104,11 +6116,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>208.2102661132812</v>
+        <v>208.2102966308594</v>
       </c>
       <c r="C214" t="n">
         <v>220.9700012207031</v>
@@ -6133,7 +6145,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6162,11 +6174,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>234.117919921875</v>
+        <v>234.1179351806641</v>
       </c>
       <c r="C216" t="n">
         <v>246.9700012207031</v>
@@ -6191,11 +6203,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>246.1570739746094</v>
+        <v>246.1570587158203</v>
       </c>
       <c r="C217" t="n">
         <v>259.6700134277344</v>
@@ -6220,11 +6232,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>252.53369140625</v>
+        <v>252.5337219238281</v>
       </c>
       <c r="C218" t="n">
         <v>264.989990234375</v>
@@ -6249,11 +6261,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>260.4054565429688</v>
+        <v>260.4053955078125</v>
       </c>
       <c r="C219" t="n">
         <v>273.25</v>
@@ -6278,7 +6290,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6307,7 +6319,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6336,7 +6348,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6365,11 +6377,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>277.8618774414062</v>
+        <v>277.8619384765625</v>
       </c>
       <c r="C223" t="n">
         <v>290.1400146484375</v>
@@ -6394,11 +6406,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>287.5022583007812</v>
+        <v>287.5022888183594</v>
       </c>
       <c r="C224" t="n">
         <v>298.7099914550781</v>
@@ -6423,11 +6435,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>288.1278991699219</v>
+        <v>288.1278686523438</v>
       </c>
       <c r="C225" t="n">
         <v>299.3599853515625</v>
@@ -6452,11 +6464,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>290.8613586425781</v>
+        <v>290.8613891601562</v>
       </c>
       <c r="C226" t="n">
         <v>302.2000122070312</v>
@@ -6481,7 +6493,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6510,11 +6522,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>274.6712951660156</v>
+        <v>274.6712646484375</v>
       </c>
       <c r="C228" t="n">
         <v>284.010009765625</v>
@@ -6539,11 +6551,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>254.8260345458984</v>
+        <v>254.8259887695312</v>
       </c>
       <c r="C229" t="n">
         <v>263.489990234375</v>
@@ -6568,11 +6580,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>249.849853515625</v>
+        <v>249.8498382568359</v>
       </c>
       <c r="C230" t="n">
         <v>256.9800109863281</v>
@@ -6597,11 +6609,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>245.5913543701172</v>
+        <v>245.5913696289062</v>
       </c>
       <c r="C231" t="n">
         <v>252.6000061035156</v>
@@ -6626,11 +6638,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>265.0169372558594</v>
+        <v>265.0169677734375</v>
       </c>
       <c r="C232" t="n">
         <v>272.5799865722656</v>
@@ -6655,11 +6667,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>266.037841796875</v>
+        <v>266.0378723144531</v>
       </c>
       <c r="C233" t="n">
         <v>272.1199951171875</v>
@@ -6684,11 +6696,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>272.2655029296875</v>
+        <v>272.2654724121094</v>
       </c>
       <c r="C234" t="n">
         <v>278.489990234375</v>
@@ -6713,11 +6725,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>285.14111328125</v>
+        <v>285.1411437988281</v>
       </c>
       <c r="C235" t="n">
         <v>291.6600036621094</v>
@@ -6742,7 +6754,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6771,7 +6783,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6800,7 +6812,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6829,7 +6841,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6858,11 +6870,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>337.1830139160156</v>
+        <v>337.1830444335938</v>
       </c>
       <c r="C240" t="n">
         <v>341.6300048828125</v>
@@ -6887,7 +6899,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6916,7 +6928,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6945,7 +6957,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6974,7 +6986,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7003,7 +7015,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7032,7 +7044,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7061,7 +7073,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7090,7 +7102,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7119,7 +7131,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7148,32 +7160,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>343.3299865722656</v>
+        <v>336.2900085449219</v>
       </c>
       <c r="C250" t="n">
-        <v>343.3299865722656</v>
+        <v>336.2900085449219</v>
       </c>
       <c r="D250" t="n">
-        <v>19911600</v>
+        <v>21481900</v>
       </c>
       <c r="E250" t="n">
         <v>16.42380042122144</v>
       </c>
       <c r="F250" t="n">
-        <v>20.90441784281814</v>
+        <v>20.47577295876029</v>
       </c>
       <c r="G250" t="n">
         <v>270430187</v>
       </c>
       <c r="H250" t="n">
-        <v>92846792471.44528</v>
+        <v>90942969897.03482</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07362935410757232</v>
+        <v>0.07943602834545982</v>
       </c>
     </row>
   </sheetData>
@@ -7205,75 +7217,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39538</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39628</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7309,13 +7321,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39719</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40120</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7351,13 +7363,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39908</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7393,13 +7405,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39909</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39999</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7435,13 +7447,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40000</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40090</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40120</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7477,13 +7489,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40272</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7519,13 +7531,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40273</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40363</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40393</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7561,13 +7573,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40364</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40454</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40484</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7603,13 +7615,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40455</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7636,7 +7648,7 @@
       <c r="I10" t="n">
         <v>6.81</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K10" t="n">
@@ -7649,13 +7661,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40636</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7682,7 +7694,7 @@
       <c r="I11" t="n">
         <v>6.919999999999999</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="K11" t="n">
@@ -7695,13 +7707,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40637</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40727</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7728,7 +7740,7 @@
       <c r="I12" t="n">
         <v>7.009999999999999</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="K12" t="n">
@@ -7741,13 +7753,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40728</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40818</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7774,7 +7786,7 @@
       <c r="I13" t="n">
         <v>7.109999999999999</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="K13" t="n">
@@ -7787,13 +7799,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40819</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7820,7 +7832,7 @@
       <c r="I14" t="n">
         <v>6.869999999999999</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="K14" t="n">
@@ -7833,13 +7845,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7866,7 +7878,7 @@
       <c r="I15" t="n">
         <v>6.8</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="K15" t="n">
@@ -7879,13 +7891,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41001</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7912,7 +7924,7 @@
       <c r="I16" t="n">
         <v>6.81</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="K16" t="n">
@@ -7925,13 +7937,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41092</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7958,7 +7970,7 @@
       <c r="I17" t="n">
         <v>6.709999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="K17" t="n">
@@ -7971,13 +7983,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41313</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8004,7 +8016,7 @@
       <c r="I18" t="n">
         <v>-0.9400000000000013</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41313</v>
       </c>
       <c r="K18" t="n">
@@ -8017,13 +8029,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8050,7 +8062,7 @@
       <c r="I19" t="n">
         <v>-0.8900000000000006</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="K19" t="n">
@@ -8063,13 +8075,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8096,7 +8108,7 @@
       <c r="I20" t="n">
         <v>-0.850000000000001</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="K20" t="n">
@@ -8109,13 +8121,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41546</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8142,7 +8154,7 @@
       <c r="I21" t="n">
         <v>-0.7100000000000006</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="K21" t="n">
@@ -8155,13 +8167,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8188,7 +8200,7 @@
       <c r="I22" t="n">
         <v>6.669999999999999</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="K22" t="n">
@@ -8201,13 +8213,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41728</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8234,7 +8246,7 @@
       <c r="I23" t="n">
         <v>6.759999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="K23" t="n">
@@ -8247,13 +8259,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41819</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8280,7 +8292,7 @@
       <c r="I24" t="n">
         <v>6.529999999999999</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="K24" t="n">
@@ -8293,13 +8305,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41910</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41934</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8326,7 +8338,7 @@
       <c r="I25" t="n">
         <v>6.749999999999998</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41934</v>
       </c>
       <c r="K25" t="n">
@@ -8339,13 +8351,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41911</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42044</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8372,7 +8384,7 @@
       <c r="I26" t="n">
         <v>7.42</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42044</v>
       </c>
       <c r="K26" t="n">
@@ -8385,13 +8397,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42099</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8418,7 +8430,7 @@
       <c r="I27" t="n">
         <v>7.85</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="K27" t="n">
@@ -8431,13 +8443,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42100</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42190</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8464,7 +8476,7 @@
       <c r="I28" t="n">
         <v>8.539999999999999</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="K28" t="n">
@@ -8477,13 +8489,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42191</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42281</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8510,7 +8522,7 @@
       <c r="I29" t="n">
         <v>8.76</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="K29" t="n">
@@ -8523,13 +8535,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42282</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42408</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8556,7 +8568,7 @@
       <c r="I30" t="n">
         <v>9.08</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42408</v>
       </c>
       <c r="K30" t="n">
@@ -8569,13 +8581,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42463</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8602,7 +8614,7 @@
       <c r="I31" t="n">
         <v>9.239999999999998</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="K31" t="n">
@@ -8615,13 +8627,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42464</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42554</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8648,7 +8660,7 @@
       <c r="I32" t="n">
         <v>9.41</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="K32" t="n">
@@ -8661,13 +8673,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42555</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42645</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8694,7 +8706,7 @@
       <c r="I33" t="n">
         <v>9.34</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="K33" t="n">
@@ -8707,13 +8719,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42646</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42772</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8740,7 +8752,7 @@
       <c r="I34" t="n">
         <v>9.52</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42772</v>
       </c>
       <c r="K34" t="n">
@@ -8753,13 +8765,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42827</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8786,7 +8798,7 @@
       <c r="I35" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="K35" t="n">
@@ -8799,13 +8811,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42828</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42918</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8832,7 +8844,7 @@
       <c r="I36" t="n">
         <v>9.712922875388896</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="K36" t="n">
@@ -8845,13 +8857,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42919</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43033</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8878,7 +8890,7 @@
       <c r="I37" t="n">
         <v>10.0229228753889</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43033</v>
       </c>
       <c r="K37" t="n">
@@ -8891,13 +8903,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43010</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43143</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8924,7 +8936,7 @@
       <c r="I38" t="n">
         <v>9.54065351874476</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43143</v>
       </c>
       <c r="K38" t="n">
@@ -8937,13 +8949,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8970,7 +8982,7 @@
       <c r="I39" t="n">
         <v>9.71422172109345</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="K39" t="n">
@@ -8983,13 +8995,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43192</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9016,7 +9028,7 @@
       <c r="I40" t="n">
         <v>9.880085474566513</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="K40" t="n">
@@ -9029,13 +9041,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43283</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9062,7 +9074,7 @@
       <c r="I41" t="n">
         <v>10.21008547456651</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="K41" t="n">
@@ -9075,13 +9087,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9108,7 +9120,7 @@
       <c r="I42" t="n">
         <v>11.16086265311197</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="K42" t="n">
@@ -9121,13 +9133,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9154,7 +9166,7 @@
       <c r="I43" t="n">
         <v>11.06839121896856</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="K43" t="n">
@@ -9167,13 +9179,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9200,7 +9212,7 @@
       <c r="I44" t="n">
         <v>11.22112600406392</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="K44" t="n">
@@ -9213,13 +9225,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43737</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9246,7 +9258,7 @@
       <c r="I45" t="n">
         <v>11.51112600406392</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="K45" t="n">
@@ -9259,13 +9271,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43871</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9292,7 +9304,7 @@
       <c r="I46" t="n">
         <v>11.97974934886823</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43871</v>
       </c>
       <c r="K46" t="n">
@@ -9305,13 +9317,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43919</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9338,7 +9350,7 @@
       <c r="I47" t="n">
         <v>11.85361393513608</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="K47" t="n">
@@ -9351,13 +9363,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43920</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44010</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9384,7 +9396,7 @@
       <c r="I48" t="n">
         <v>11.26030137132844</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K48" t="n">
@@ -9397,13 +9409,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44011</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44101</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9430,7 +9442,7 @@
       <c r="I49" t="n">
         <v>11.02392811951019</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="K49" t="n">
@@ -9443,13 +9455,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44102</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9476,7 +9488,7 @@
       <c r="I50" t="n">
         <v>10.99701493532011</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="K50" t="n">
@@ -9489,13 +9501,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44290</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9522,7 +9534,7 @@
       <c r="I51" t="n">
         <v>11.04453943278144</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="K51" t="n">
@@ -9535,13 +9547,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44291</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44381</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9568,7 +9580,7 @@
       <c r="I52" t="n">
         <v>11.47783324197062</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="K52" t="n">
@@ -9581,13 +9593,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44382</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44472</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9614,7 +9626,7 @@
       <c r="I53" t="n">
         <v>11.64119887980195</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="K53" t="n">
@@ -9627,13 +9639,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44473</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9660,7 +9672,7 @@
       <c r="I54" t="n">
         <v>11.53666392348695</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="K54" t="n">
@@ -9673,13 +9685,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44654</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9706,7 +9718,7 @@
       <c r="I55" t="n">
         <v>11.66190766785453</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="K55" t="n">
@@ -9719,13 +9731,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44655</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44745</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9752,7 +9764,7 @@
       <c r="I56" t="n">
         <v>11.79648574902537</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="K56" t="n">
@@ -9765,13 +9777,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44746</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44836</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9798,7 +9810,7 @@
       <c r="I57" t="n">
         <v>11.99309229492536</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="K57" t="n">
@@ -9811,13 +9823,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44837</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9844,7 +9856,7 @@
       <c r="I58" t="n">
         <v>12.18358666448063</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="K58" t="n">
@@ -9857,13 +9869,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45018</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9890,7 +9902,7 @@
       <c r="I59" t="n">
         <v>12.21460839659109</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="K59" t="n">
@@ -9903,13 +9915,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45019</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45109</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9936,7 +9948,7 @@
       <c r="I60" t="n">
         <v>12.17312656479026</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="K60" t="n">
@@ -9949,13 +9961,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9982,7 +9994,7 @@
       <c r="I61" t="n">
         <v>11.95234915829166</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="K61" t="n">
@@ -9995,13 +10007,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45201</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10028,7 +10040,7 @@
       <c r="I62" t="n">
         <v>12.0311078401494</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="K62" t="n">
@@ -10041,13 +10053,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10074,7 +10086,7 @@
       <c r="I63" t="n">
         <v>12.27679139354368</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="K63" t="n">
@@ -10087,13 +10099,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10120,7 +10132,7 @@
       <c r="I64" t="n">
         <v>12.83084682262583</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="K64" t="n">
@@ -10133,13 +10145,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45564</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10166,7 +10178,7 @@
       <c r="I65" t="n">
         <v>13.13469733774567</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="K65" t="n">
@@ -10179,13 +10191,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10212,7 +10224,7 @@
       <c r="I66" t="n">
         <v>13.62692182736997</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="K66" t="n">
@@ -10225,13 +10237,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45746</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10258,7 +10270,7 @@
       <c r="I67" t="n">
         <v>14.40027409473396</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="K67" t="n">
@@ -10271,13 +10283,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45837</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10304,7 +10316,7 @@
       <c r="I68" t="n">
         <v>14.88407671315175</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="K68" t="n">
@@ -10317,13 +10329,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10350,7 +10362,7 @@
       <c r="I69" t="n">
         <v>15.42164763036391</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="K69" t="n">
@@ -10363,13 +10375,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45929</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10396,7 +10408,7 @@
       <c r="I70" t="n">
         <v>15.48013724207438</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="K70" t="n">
@@ -10409,13 +10421,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10442,7 +10454,7 @@
       <c r="I71" t="n">
         <v>15.92625737743026</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="K71" t="n">
@@ -10455,13 +10467,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10482,7 +10494,7 @@
       <c r="I72" t="n">
         <v>16.42380042122144</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K72" t="n">
@@ -10519,52 +10531,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39999</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="C2" t="n">
@@ -10593,10 +10605,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40090</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40120</v>
       </c>
       <c r="C3" t="n">
@@ -10625,10 +10637,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40228</v>
       </c>
       <c r="C4" t="n">
@@ -10657,10 +10669,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40272</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="C5" t="n">
@@ -10689,10 +10701,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40363</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40393</v>
       </c>
       <c r="C6" t="n">
@@ -10721,10 +10733,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40454</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40484</v>
       </c>
       <c r="C7" t="n">
@@ -10753,10 +10765,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40573</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="C8" t="n">
@@ -10785,10 +10797,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40636</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="C9" t="n">
@@ -10817,10 +10829,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40727</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="C10" t="n">
@@ -10849,10 +10861,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40818</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="C11" t="n">
@@ -10881,10 +10893,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40937</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="C12" t="n">
@@ -10913,10 +10925,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="C13" t="n">
@@ -10945,10 +10957,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="C14" t="n">
@@ -10977,10 +10989,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="C15" t="n">
@@ -11009,10 +11021,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41301</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41313</v>
       </c>
       <c r="C16" t="n">
@@ -11041,10 +11053,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="C17" t="n">
@@ -11073,10 +11085,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="C18" t="n">
@@ -11105,10 +11117,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41546</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="C19" t="n">
@@ -11137,10 +11149,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41665</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="C20" t="n">
@@ -11169,10 +11181,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41728</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="C21" t="n">
@@ -11201,10 +11213,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41819</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="C22" t="n">
@@ -11233,10 +11245,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41910</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41934</v>
       </c>
       <c r="C23" t="n">
@@ -11265,10 +11277,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42036</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42044</v>
       </c>
       <c r="C24" t="n">
@@ -11297,10 +11309,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42099</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="C25" t="n">
@@ -11329,10 +11341,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42190</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="C26" t="n">
@@ -11361,10 +11373,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42281</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="C27" t="n">
@@ -11393,10 +11405,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42408</v>
       </c>
       <c r="C28" t="n">
@@ -11425,10 +11437,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42463</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="C29" t="n">
@@ -11457,10 +11469,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42554</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="C30" t="n">
@@ -11489,10 +11501,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42645</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="C31" t="n">
@@ -11521,10 +11533,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42764</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42772</v>
       </c>
       <c r="C32" t="n">
@@ -11553,10 +11565,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42827</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="C33" t="n">
@@ -11585,10 +11597,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42918</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="C34" t="n">
@@ -11617,10 +11629,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43033</v>
       </c>
       <c r="C35" t="n">
@@ -11649,10 +11661,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43128</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43143</v>
       </c>
       <c r="C36" t="n">
@@ -11681,10 +11693,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="C37" t="n">
@@ -11713,10 +11725,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="C38" t="n">
@@ -11745,10 +11757,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="C39" t="n">
@@ -11777,10 +11789,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43492</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="C40" t="n">
@@ -11809,10 +11821,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="C41" t="n">
@@ -11841,10 +11853,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="C42" t="n">
@@ -11873,10 +11885,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43737</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="C43" t="n">
@@ -11905,10 +11917,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43856</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43871</v>
       </c>
       <c r="C44" t="n">
@@ -11937,10 +11949,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43919</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C45" t="n">
@@ -11969,10 +11981,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44010</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C46" t="n">
@@ -12001,10 +12013,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44101</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="C47" t="n">
@@ -12033,10 +12045,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="C48" t="n">
@@ -12065,10 +12077,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44290</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="C49" t="n">
@@ -12097,10 +12109,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44381</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="C50" t="n">
@@ -12129,10 +12141,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44472</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="C51" t="n">
@@ -12161,10 +12173,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44591</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="C52" t="n">
@@ -12193,10 +12205,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44654</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="C53" t="n">
@@ -12225,10 +12237,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44745</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="C54" t="n">
@@ -12257,10 +12269,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44836</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="C55" t="n">
@@ -12289,10 +12301,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44955</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="C56" t="n">
@@ -12321,10 +12333,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45018</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="C57" t="n">
@@ -12353,10 +12365,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45109</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="C58" t="n">
@@ -12385,10 +12397,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="C59" t="n">
@@ -12417,10 +12429,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45319</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="C60" t="n">
@@ -12449,10 +12461,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="C61" t="n">
@@ -12481,10 +12493,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="C62" t="n">
@@ -12513,10 +12525,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45564</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="C63" t="n">
@@ -12545,10 +12557,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45683</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="C64" t="n">
@@ -12577,10 +12589,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45746</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="C65" t="n">
@@ -12609,10 +12621,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45837</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="C66" t="n">
@@ -12641,10 +12653,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="C67" t="n">
@@ -12673,10 +12685,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="C68" t="n">
@@ -12705,10 +12717,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="C69" t="n">
@@ -12755,12 +12767,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -12810,7 +12822,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2010, 2015, 2017</t>
+          <t>2010, 2015, 2016, 2017</t>
         </is>
       </c>
     </row>
@@ -12821,7 +12833,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">

--- a/salidas/empresas/GD.xlsx
+++ b/salidas/empresas/GD.xlsx
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>39.16244506835938</v>
+        <v>39.16244888305664</v>
       </c>
       <c r="C3" t="n">
         <v>61.6349983215332</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>40.6524543762207</v>
+        <v>40.65243911743164</v>
       </c>
       <c r="C4" t="n">
         <v>63.97999954223633</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>40.57979583740234</v>
+        <v>40.57979965209961</v>
       </c>
       <c r="C6" t="n">
         <v>63.63999938964844</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>41.74031066894531</v>
+        <v>41.74030685424805</v>
       </c>
       <c r="C7" t="n">
         <v>65.45999908447266</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>42.88631820678711</v>
+        <v>42.88631439208984</v>
       </c>
       <c r="C8" t="n">
         <v>67.01999664306641</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>43.22548294067383</v>
+        <v>43.22548675537109</v>
       </c>
       <c r="C9" t="n">
         <v>67.55000305175781</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>45.86186599731445</v>
+        <v>45.86186981201172</v>
       </c>
       <c r="C10" t="n">
         <v>71.66999816894531</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>45.63871383666992</v>
+        <v>45.63870239257812</v>
       </c>
       <c r="C11" t="n">
         <v>71.09999847412109</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>48.03940200805664</v>
+        <v>48.03938674926758</v>
       </c>
       <c r="C12" t="n">
         <v>74.83999633789062</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>47.72485733032227</v>
+        <v>47.72487640380859</v>
       </c>
       <c r="C13" t="n">
         <v>74.34999847412109</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>50.72227478027344</v>
+        <v>50.72228622436523</v>
       </c>
       <c r="C17" t="n">
         <v>78.5</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>51.84657669067383</v>
+        <v>51.84658050537109</v>
       </c>
       <c r="C18" t="n">
         <v>80.23999786376953</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>50.5413703918457</v>
+        <v>50.54136276245117</v>
       </c>
       <c r="C19" t="n">
         <v>78.22000122070312</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>50.95001602172852</v>
+        <v>50.95001220703125</v>
       </c>
       <c r="C20" t="n">
         <v>78.55999755859375</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>50.95001602172852</v>
+        <v>50.95001220703125</v>
       </c>
       <c r="C21" t="n">
         <v>78.55999755859375</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>54.78295135498047</v>
+        <v>54.78292846679688</v>
       </c>
       <c r="C22" t="n">
         <v>84.47000122070312</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>59.19800186157227</v>
+        <v>59.19797134399414</v>
       </c>
       <c r="C23" t="n">
         <v>90.95999908447266</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>57.77922821044922</v>
+        <v>57.77922439575195</v>
       </c>
       <c r="C24" t="n">
         <v>88.77999877929688</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>57.91587066650391</v>
+        <v>57.91587829589844</v>
       </c>
       <c r="C25" t="n">
         <v>88.98999786376953</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>55.20091247558594</v>
+        <v>55.20088195800781</v>
       </c>
       <c r="C26" t="n">
         <v>84.52999877929688</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>53.45076370239258</v>
+        <v>53.45077514648438</v>
       </c>
       <c r="C27" t="n">
         <v>81.84999847412109</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>54.44336700439453</v>
+        <v>54.44338989257812</v>
       </c>
       <c r="C28" t="n">
         <v>83.37000274658203</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>59.29198455810547</v>
+        <v>59.29196929931641</v>
       </c>
       <c r="C29" t="n">
         <v>90.41999816894531</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>60.42642593383789</v>
+        <v>60.42641067504883</v>
       </c>
       <c r="C30" t="n">
         <v>92.15000152587891</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>55.21327209472656</v>
+        <v>55.21326065063477</v>
       </c>
       <c r="C31" t="n">
         <v>84.19999694824219</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>58.69663619995117</v>
+        <v>58.69661712646484</v>
       </c>
       <c r="C32" t="n">
         <v>89.13999938964844</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>60.77743911743164</v>
+        <v>60.77740859985352</v>
       </c>
       <c r="C33" t="n">
         <v>92.30000305175781</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>48.47705459594727</v>
+        <v>48.47706604003906</v>
       </c>
       <c r="C34" t="n">
         <v>73.62000274658203</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>39.93417739868164</v>
+        <v>39.93420028686523</v>
       </c>
       <c r="C35" t="n">
         <v>60.31999969482422</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>34.20753860473633</v>
+        <v>34.20754623413086</v>
       </c>
       <c r="C36" t="n">
         <v>51.66999816894531</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>37.79756164550781</v>
+        <v>37.79755783081055</v>
       </c>
       <c r="C38" t="n">
         <v>56.72999954223633</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>29.19600486755371</v>
+        <v>29.19600677490234</v>
       </c>
       <c r="C39" t="n">
         <v>43.81999969482422</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>34.71577835083008</v>
+        <v>34.71577072143555</v>
       </c>
       <c r="C41" t="n">
         <v>51.66999816894531</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>38.22968292236328</v>
+        <v>38.22969436645508</v>
       </c>
       <c r="C42" t="n">
         <v>56.90000152587891</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>37.46490478515625</v>
+        <v>37.46492004394531</v>
       </c>
       <c r="C43" t="n">
         <v>55.38999938964844</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>37.46490478515625</v>
+        <v>37.46492004394531</v>
       </c>
       <c r="C44" t="n">
         <v>55.38999938964844</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>40.03516387939453</v>
+        <v>40.03517150878906</v>
       </c>
       <c r="C45" t="n">
         <v>59.18999862670898</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>43.69441986083984</v>
+        <v>43.69440460205078</v>
       </c>
       <c r="C46" t="n">
         <v>64.59999847412109</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>42.65517807006836</v>
+        <v>42.65517425537109</v>
       </c>
       <c r="C47" t="n">
         <v>62.70000076293945</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>44.8321533203125</v>
+        <v>44.83215713500977</v>
       </c>
       <c r="C48" t="n">
         <v>65.90000152587891</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>46.37643432617188</v>
+        <v>46.37644195556641</v>
       </c>
       <c r="C49" t="n">
         <v>68.16999816894531</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>45.72560501098633</v>
+        <v>45.72561645507812</v>
       </c>
       <c r="C50" t="n">
         <v>66.84999847412109</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>52.80503845214844</v>
+        <v>52.8050537109375</v>
       </c>
       <c r="C52" t="n">
         <v>77.19999694824219</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>52.51539611816406</v>
+        <v>52.51541137695312</v>
       </c>
       <c r="C53" t="n">
         <v>76.36000061035156</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>46.69716644287109</v>
+        <v>46.69718551635742</v>
       </c>
       <c r="C54" t="n">
         <v>67.90000152587891</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>40.56037139892578</v>
+        <v>40.56037902832031</v>
       </c>
       <c r="C55" t="n">
         <v>58.56000137329102</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>38.69720458984375</v>
+        <v>38.69721221923828</v>
       </c>
       <c r="C57" t="n">
         <v>55.86999893188477</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>43.50406265258789</v>
+        <v>43.50404739379883</v>
       </c>
       <c r="C58" t="n">
         <v>62.81000137329102</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>47.49652099609375</v>
+        <v>47.49651336669922</v>
       </c>
       <c r="C59" t="n">
         <v>68.12000274658203</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>46.08108901977539</v>
+        <v>46.08110046386719</v>
       </c>
       <c r="C60" t="n">
         <v>66.08999633789062</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>49.47669982910156</v>
+        <v>49.47666931152344</v>
       </c>
       <c r="C61" t="n">
         <v>70.95999908447266</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>52.88420486450195</v>
+        <v>52.88421249389648</v>
       </c>
       <c r="C62" t="n">
         <v>75.40000152587891</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>53.69783020019531</v>
+        <v>53.69782638549805</v>
       </c>
       <c r="C64" t="n">
         <v>76.55999755859375</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>51.39845657348633</v>
+        <v>51.39849472045898</v>
       </c>
       <c r="C65" t="n">
         <v>72.81999969482422</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>52.38664627075195</v>
+        <v>52.38661193847656</v>
       </c>
       <c r="C66" t="n">
         <v>74.22000122070312</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>52.93579483032227</v>
+        <v>52.93578338623047</v>
       </c>
       <c r="C67" t="n">
         <v>74.51999664306641</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>48.4036979675293</v>
+        <v>48.40370559692383</v>
       </c>
       <c r="C68" t="n">
         <v>68.13999938964844</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>45.51966094970703</v>
+        <v>45.51965713500977</v>
       </c>
       <c r="C69" t="n">
         <v>64.08000183105469</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>40.41219329833984</v>
+        <v>40.41218185424805</v>
       </c>
       <c r="C70" t="n">
         <v>56.88999938964844</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>45.97616958618164</v>
+        <v>45.97616577148438</v>
       </c>
       <c r="C71" t="n">
         <v>64.19000244140625</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>47.3155632019043</v>
+        <v>47.31555557250977</v>
       </c>
       <c r="C72" t="n">
         <v>66.05999755859375</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>49.86394119262695</v>
+        <v>49.86395263671875</v>
       </c>
       <c r="C74" t="n">
         <v>69.16000366210938</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>52.90653228759766</v>
+        <v>52.90653610229492</v>
       </c>
       <c r="C76" t="n">
         <v>73.37999725341797</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>49.0269660949707</v>
+        <v>49.02698516845703</v>
       </c>
       <c r="C77" t="n">
         <v>67.5</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>46.49209594726562</v>
+        <v>46.49209213256836</v>
       </c>
       <c r="C78" t="n">
         <v>64.01000213623047</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>47.90842819213867</v>
+        <v>47.90840911865234</v>
       </c>
       <c r="C79" t="n">
         <v>65.95999908447266</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>47.9517822265625</v>
+        <v>47.95177459716797</v>
       </c>
       <c r="C81" t="n">
         <v>65.51000213623047</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>48.39828491210938</v>
+        <v>48.39828109741211</v>
       </c>
       <c r="C82" t="n">
         <v>66.12000274658203</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>50.21345138549805</v>
+        <v>50.21347427368164</v>
       </c>
       <c r="C83" t="n">
         <v>68.08000183105469</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>49.04811477661133</v>
+        <v>49.0481071472168</v>
       </c>
       <c r="C84" t="n">
         <v>66.5</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>51.47725296020508</v>
+        <v>51.47724914550781</v>
       </c>
       <c r="C85" t="n">
         <v>69.26999664306641</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>49.27013397216797</v>
+        <v>49.2701416015625</v>
       </c>
       <c r="C86" t="n">
         <v>66.30000305175781</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>50.51115798950195</v>
+        <v>50.51118469238281</v>
       </c>
       <c r="C87" t="n">
         <v>67.97000122070312</v>
@@ -2488,7 +2488,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>52.39875030517578</v>
+        <v>52.39875411987305</v>
       </c>
       <c r="C88" t="n">
         <v>70.51000213623047</v>
@@ -2542,7 +2542,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>57.76260757446289</v>
+        <v>57.76260375976562</v>
       </c>
       <c r="C90" t="n">
         <v>77.09999847412109</v>
@@ -2596,7 +2596,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>64.39230346679688</v>
+        <v>64.392333984375</v>
       </c>
       <c r="C92" t="n">
         <v>85.33999633789062</v>
@@ -2623,7 +2623,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>62.81532669067383</v>
+        <v>62.81533432006836</v>
       </c>
       <c r="C93" t="n">
         <v>83.25</v>
@@ -2677,7 +2677,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>65.79932403564453</v>
+        <v>65.79933166503906</v>
       </c>
       <c r="C95" t="n">
         <v>86.62999725341797</v>
@@ -2704,7 +2704,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>69.61985015869141</v>
+        <v>69.61984252929688</v>
       </c>
       <c r="C96" t="n">
         <v>91.66000366210938</v>
@@ -2731,7 +2731,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>72.57447052001953</v>
+        <v>72.57444763183594</v>
       </c>
       <c r="C97" t="n">
         <v>95.55000305175781</v>
@@ -2785,7 +2785,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>83.68886566162109</v>
+        <v>83.68888854980469</v>
       </c>
       <c r="C99" t="n">
         <v>109.5400009155273</v>
@@ -2814,7 +2814,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>83.21519470214844</v>
+        <v>83.21521759033203</v>
       </c>
       <c r="C100" t="n">
         <v>108.9199981689453</v>
@@ -2843,7 +2843,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>84.11033630371094</v>
+        <v>84.11034393310547</v>
       </c>
       <c r="C101" t="n">
         <v>109.4499969482422</v>
@@ -2872,7 +2872,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>90.77308654785156</v>
+        <v>90.7730712890625</v>
       </c>
       <c r="C102" t="n">
         <v>118.120002746582</v>
@@ -2901,7 +2901,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>89.56655883789062</v>
+        <v>89.56657409667969</v>
       </c>
       <c r="C103" t="n">
         <v>116.5500030517578</v>
@@ -2930,7 +2930,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>90.21551513671875</v>
+        <v>90.21553039550781</v>
       </c>
       <c r="C104" t="n">
         <v>116.7699966430664</v>
@@ -2959,7 +2959,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>95.22193145751953</v>
+        <v>95.221923828125</v>
       </c>
       <c r="C105" t="n">
         <v>123.25</v>
@@ -2988,7 +2988,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>98.18868255615234</v>
+        <v>98.18869018554688</v>
       </c>
       <c r="C106" t="n">
         <v>127.0899963378906</v>
@@ -3017,7 +3017,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>108.5349655151367</v>
+        <v>108.5350036621094</v>
       </c>
       <c r="C107" t="n">
         <v>139.7599945068359</v>
@@ -3046,7 +3046,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>112.8838119506836</v>
+        <v>112.8838424682617</v>
       </c>
       <c r="C108" t="n">
         <v>145.3600006103516</v>
@@ -3075,7 +3075,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>106.8730926513672</v>
+        <v>106.8731002807617</v>
       </c>
       <c r="C109" t="n">
         <v>137.6199951171875</v>
@@ -3104,7 +3104,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>103.9159698486328</v>
+        <v>103.9159545898438</v>
       </c>
       <c r="C110" t="n">
         <v>133.2100067138672</v>
@@ -3133,7 +3133,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>108.2610473632812</v>
+        <v>108.2610549926758</v>
       </c>
       <c r="C111" t="n">
         <v>138.7799987792969</v>
@@ -3162,7 +3162,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>105.8817672729492</v>
+        <v>105.8817749023438</v>
       </c>
       <c r="C112" t="n">
         <v>135.7299957275391</v>
@@ -3191,7 +3191,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>107.6724624633789</v>
+        <v>107.6724700927734</v>
       </c>
       <c r="C113" t="n">
         <v>137.3200073242188</v>
@@ -3220,7 +3220,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>109.899284362793</v>
+        <v>109.8992919921875</v>
       </c>
       <c r="C114" t="n">
         <v>140.1600036621094</v>
@@ -3249,7 +3249,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>111.6420593261719</v>
+        <v>111.6420669555664</v>
       </c>
       <c r="C115" t="n">
         <v>141.6900024414062</v>
@@ -3307,7 +3307,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>111.9099426269531</v>
+        <v>111.9099578857422</v>
       </c>
       <c r="C117" t="n">
         <v>142.0299987792969</v>
@@ -3336,7 +3336,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>108.695182800293</v>
+        <v>108.6951904296875</v>
       </c>
       <c r="C118" t="n">
         <v>137.9499969482422</v>
@@ -3365,7 +3365,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>117.6480255126953</v>
+        <v>117.6480407714844</v>
       </c>
       <c r="C119" t="n">
         <v>148.5800018310547</v>
@@ -3423,7 +3423,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>108.7638549804688</v>
+        <v>108.7638702392578</v>
       </c>
       <c r="C121" t="n">
         <v>137.3600006103516</v>
@@ -3452,7 +3452,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>106.4757537841797</v>
+        <v>106.4757385253906</v>
       </c>
       <c r="C122" t="n">
         <v>133.7700042724609</v>
@@ -3510,7 +3510,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>104.5654602050781</v>
+        <v>104.5654525756836</v>
       </c>
       <c r="C124" t="n">
         <v>131.3699951171875</v>
@@ -3539,7 +3539,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>112.5019912719727</v>
+        <v>112.5019607543945</v>
       </c>
       <c r="C125" t="n">
         <v>140.5200042724609</v>
@@ -3568,7 +3568,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>113.5827941894531</v>
+        <v>113.5827865600586</v>
       </c>
       <c r="C126" t="n">
         <v>141.8699951171875</v>
@@ -3597,7 +3597,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>112.1133346557617</v>
+        <v>112.1133499145508</v>
       </c>
       <c r="C127" t="n">
         <v>139.2400054931641</v>
@@ -3626,7 +3626,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>118.2730178833008</v>
+        <v>118.2729644775391</v>
       </c>
       <c r="C128" t="n">
         <v>146.8899993896484</v>
@@ -3655,7 +3655,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>122.5645751953125</v>
+        <v>122.564582824707</v>
       </c>
       <c r="C129" t="n">
         <v>152.2200012207031</v>
@@ -3684,7 +3684,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>124.931770324707</v>
+        <v>124.9318389892578</v>
       </c>
       <c r="C130" t="n">
         <v>155.1600036621094</v>
@@ -3713,7 +3713,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>121.9766616821289</v>
+        <v>121.9766693115234</v>
       </c>
       <c r="C131" t="n">
         <v>150.7400054931641</v>
@@ -3742,7 +3742,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>141.8906707763672</v>
+        <v>141.8907012939453</v>
       </c>
       <c r="C132" t="n">
         <v>175.3500061035156</v>
@@ -3800,7 +3800,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>147.1629028320312</v>
+        <v>147.1629333496094</v>
       </c>
       <c r="C134" t="n">
         <v>181.0800018310547</v>
@@ -3829,7 +3829,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>154.2577667236328</v>
+        <v>154.2577209472656</v>
       </c>
       <c r="C135" t="n">
         <v>189.8099975585938</v>
@@ -3887,7 +3887,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>158.2001495361328</v>
+        <v>158.2001800537109</v>
       </c>
       <c r="C137" t="n">
         <v>193.7899932861328</v>
@@ -3916,7 +3916,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>165.9228210449219</v>
+        <v>165.9227905273438</v>
       </c>
       <c r="C138" t="n">
         <v>203.25</v>
@@ -3945,7 +3945,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>161.7186737060547</v>
+        <v>161.7186431884766</v>
       </c>
       <c r="C139" t="n">
         <v>198.1000061035156</v>
@@ -3974,7 +3974,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>160.9508819580078</v>
+        <v>160.9508666992188</v>
       </c>
       <c r="C140" t="n">
         <v>196.3300018310547</v>
@@ -4003,7 +4003,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>165.0662078857422</v>
+        <v>165.0662231445312</v>
       </c>
       <c r="C141" t="n">
         <v>201.3500061035156</v>
@@ -4061,7 +4061,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>167.0666351318359</v>
+        <v>167.0666961669922</v>
       </c>
       <c r="C143" t="n">
         <v>202.9799957275391</v>
@@ -4090,7 +4090,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>170.507080078125</v>
+        <v>170.5070953369141</v>
       </c>
       <c r="C144" t="n">
         <v>207.1600036621094</v>
@@ -4119,7 +4119,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>167.4535369873047</v>
+        <v>167.4535064697266</v>
       </c>
       <c r="C145" t="n">
         <v>203.4499969482422</v>
@@ -4148,7 +4148,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>183.857177734375</v>
+        <v>183.8571624755859</v>
       </c>
       <c r="C146" t="n">
         <v>222.4799957275391</v>
@@ -4206,7 +4206,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>182.5514221191406</v>
+        <v>182.5514526367188</v>
       </c>
       <c r="C148" t="n">
         <v>220.8999938964844</v>
@@ -4264,7 +4264,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>167.4126281738281</v>
+        <v>167.4125823974609</v>
       </c>
       <c r="C150" t="n">
         <v>201.7100067138672</v>
@@ -4293,7 +4293,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>154.714111328125</v>
+        <v>154.7140808105469</v>
       </c>
       <c r="C151" t="n">
         <v>186.4100036621094</v>
@@ -4351,7 +4351,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>161.3063507080078</v>
+        <v>161.306396484375</v>
       </c>
       <c r="C153" t="n">
         <v>193.3999938964844</v>
@@ -4380,7 +4380,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>170.7479400634766</v>
+        <v>170.7479095458984</v>
       </c>
       <c r="C154" t="n">
         <v>204.7200012207031</v>
@@ -4438,7 +4438,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>154.9089050292969</v>
+        <v>154.9088745117188</v>
       </c>
       <c r="C156" t="n">
         <v>184.8899993896484</v>
@@ -4467,7 +4467,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>131.7174377441406</v>
+        <v>131.7173919677734</v>
       </c>
       <c r="C157" t="n">
         <v>157.2100067138672</v>
@@ -4525,7 +4525,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>143.4331359863281</v>
+        <v>143.43310546875</v>
       </c>
       <c r="C159" t="n">
         <v>170.2200012207031</v>
@@ -4554,7 +4554,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>142.6410217285156</v>
+        <v>142.6410522460938</v>
       </c>
       <c r="C160" t="n">
         <v>169.2799987792969</v>
@@ -4583,7 +4583,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>151.5079193115234</v>
+        <v>151.5078735351562</v>
       </c>
       <c r="C161" t="n">
         <v>178.7200012207031</v>
@@ -4612,7 +4612,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>136.3333892822266</v>
+        <v>136.3333740234375</v>
       </c>
       <c r="C162" t="n">
         <v>160.8200073242188</v>
@@ -4670,7 +4670,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>158.5093688964844</v>
+        <v>158.5093536376953</v>
       </c>
       <c r="C164" t="n">
         <v>185.9400024414062</v>
@@ -4699,7 +4699,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>163.0530548095703</v>
+        <v>163.0530395507812</v>
       </c>
       <c r="C165" t="n">
         <v>191.2700042724609</v>
@@ -4728,7 +4728,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>155.7728881835938</v>
+        <v>155.7728576660156</v>
       </c>
       <c r="C166" t="n">
         <v>182.7299957275391</v>
@@ -4786,7 +4786,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>155.8266906738281</v>
+        <v>155.8266754150391</v>
       </c>
       <c r="C168" t="n">
         <v>181.7400054931641</v>
@@ -4815,7 +4815,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>151.2052459716797</v>
+        <v>151.2051544189453</v>
       </c>
       <c r="C169" t="n">
         <v>176.3500061035156</v>
@@ -4844,7 +4844,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>151.2745361328125</v>
+        <v>151.2745819091797</v>
       </c>
       <c r="C170" t="n">
         <v>175.4400024414062</v>
@@ -4873,7 +4873,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>137.6940155029297</v>
+        <v>137.6939849853516</v>
       </c>
       <c r="C171" t="n">
         <v>159.6900024414062</v>
@@ -4902,7 +4902,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>114.0853652954102</v>
+        <v>114.0853805541992</v>
       </c>
       <c r="C172" t="n">
         <v>132.3099975585938</v>
@@ -4931,7 +4931,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>113.5575714111328</v>
+        <v>113.5575866699219</v>
       </c>
       <c r="C173" t="n">
         <v>130.6199951171875</v>
@@ -4960,7 +4960,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>127.6501083374023</v>
+        <v>127.6501312255859</v>
       </c>
       <c r="C174" t="n">
         <v>146.8300018310547</v>
@@ -4989,7 +4989,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>129.9365692138672</v>
+        <v>129.9365844726562</v>
       </c>
       <c r="C175" t="n">
         <v>149.4600067138672</v>
@@ -5018,7 +5018,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>128.5177459716797</v>
+        <v>128.5177917480469</v>
       </c>
       <c r="C176" t="n">
         <v>146.7400054931641</v>
@@ -5047,7 +5047,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>130.8036193847656</v>
+        <v>130.8036346435547</v>
       </c>
       <c r="C177" t="n">
         <v>149.3500061035156</v>
@@ -5076,7 +5076,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>121.2397003173828</v>
+        <v>121.2396774291992</v>
       </c>
       <c r="C178" t="n">
         <v>138.4299926757812</v>
@@ -5105,7 +5105,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>115.9014358520508</v>
+        <v>115.9014129638672</v>
       </c>
       <c r="C179" t="n">
         <v>131.3300018310547</v>
@@ -5163,7 +5163,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>131.3367004394531</v>
+        <v>131.3367309570312</v>
       </c>
       <c r="C181" t="n">
         <v>148.8200073242188</v>
@@ -5192,7 +5192,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>130.3877868652344</v>
+        <v>130.3878173828125</v>
       </c>
       <c r="C182" t="n">
         <v>146.6799926757812</v>
@@ -5250,7 +5250,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>161.3935699462891</v>
+        <v>161.3935546875</v>
       </c>
       <c r="C184" t="n">
         <v>181.5599975585938</v>
@@ -5279,7 +5279,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>170.1965942382812</v>
+        <v>170.1965789794922</v>
       </c>
       <c r="C185" t="n">
         <v>190.2299957275391</v>
@@ -5308,7 +5308,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>169.9102783203125</v>
+        <v>169.9103088378906</v>
       </c>
       <c r="C186" t="n">
         <v>189.9100036621094</v>
@@ -5337,7 +5337,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>168.43408203125</v>
+        <v>168.4340515136719</v>
       </c>
       <c r="C187" t="n">
         <v>188.2599945068359</v>
@@ -5366,7 +5366,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>176.5014953613281</v>
+        <v>176.5014495849609</v>
       </c>
       <c r="C188" t="n">
         <v>196.0299987792969</v>
@@ -5395,7 +5395,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>180.3550720214844</v>
+        <v>180.3551177978516</v>
       </c>
       <c r="C189" t="n">
         <v>200.3099975585938</v>
@@ -5424,7 +5424,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>176.5014953613281</v>
+        <v>176.5014495849609</v>
       </c>
       <c r="C190" t="n">
         <v>196.0299987792969</v>
@@ -5453,7 +5453,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>183.6481781005859</v>
+        <v>183.6482543945312</v>
       </c>
       <c r="C191" t="n">
         <v>202.75</v>
@@ -5482,7 +5482,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>171.1665191650391</v>
+        <v>171.1664886474609</v>
       </c>
       <c r="C192" t="n">
         <v>188.9700012207031</v>
@@ -5540,7 +5540,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>193.2021942138672</v>
+        <v>193.2022094726562</v>
       </c>
       <c r="C194" t="n">
         <v>212.1000061035156</v>
@@ -5598,7 +5598,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>219.6911926269531</v>
+        <v>219.6911773681641</v>
       </c>
       <c r="C196" t="n">
         <v>241.1799926757812</v>
@@ -5627,7 +5627,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>216.5890197753906</v>
+        <v>216.5890045166016</v>
       </c>
       <c r="C197" t="n">
         <v>236.5299987792969</v>
@@ -5656,7 +5656,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>205.9486694335938</v>
+        <v>205.9486389160156</v>
       </c>
       <c r="C198" t="n">
         <v>224.9100036621094</v>
@@ -5685,7 +5685,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>203.7680816650391</v>
+        <v>203.76806640625</v>
       </c>
       <c r="C199" t="n">
         <v>221.25</v>
@@ -5714,7 +5714,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>208.7598114013672</v>
+        <v>208.7598266601562</v>
       </c>
       <c r="C200" t="n">
         <v>226.6699981689453</v>
@@ -5743,7 +5743,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>210.8412628173828</v>
+        <v>210.8412475585938</v>
       </c>
       <c r="C201" t="n">
         <v>228.9299926757812</v>
@@ -5772,7 +5772,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>195.4055480957031</v>
+        <v>195.405517578125</v>
       </c>
       <c r="C202" t="n">
         <v>212.1699981689453</v>
@@ -5801,7 +5801,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>231.3481597900391</v>
+        <v>231.3481750488281</v>
       </c>
       <c r="C203" t="n">
         <v>249.8000030517578</v>
@@ -5830,7 +5830,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>233.7468566894531</v>
+        <v>233.7468109130859</v>
       </c>
       <c r="C204" t="n">
         <v>252.3899993896484</v>
@@ -5859,7 +5859,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>229.7829742431641</v>
+        <v>229.7829895019531</v>
       </c>
       <c r="C205" t="n">
         <v>248.1100006103516</v>
@@ -5917,7 +5917,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>212.2032775878906</v>
+        <v>212.2032623291016</v>
       </c>
       <c r="C207" t="n">
         <v>227.9100036621094</v>
@@ -5946,7 +5946,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>212.4826202392578</v>
+        <v>212.4825897216797</v>
       </c>
       <c r="C208" t="n">
         <v>228.2100067138672</v>
@@ -5975,7 +5975,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>204.4701690673828</v>
+        <v>204.4701385498047</v>
       </c>
       <c r="C209" t="n">
         <v>218.3399963378906</v>
@@ -6004,7 +6004,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>191.2096710205078</v>
+        <v>191.2096405029297</v>
       </c>
       <c r="C210" t="n">
         <v>204.1799926757812</v>
@@ -6062,7 +6062,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>210.6695404052734</v>
+        <v>210.6695861816406</v>
       </c>
       <c r="C212" t="n">
         <v>223.5800018310547</v>
@@ -6091,7 +6091,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>213.5528717041016</v>
+        <v>213.5528869628906</v>
       </c>
       <c r="C213" t="n">
         <v>226.6399993896484</v>
@@ -6120,7 +6120,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>208.2102966308594</v>
+        <v>208.2102813720703</v>
       </c>
       <c r="C214" t="n">
         <v>220.9700012207031</v>
@@ -6149,7 +6149,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>228.7524566650391</v>
+        <v>228.7524871826172</v>
       </c>
       <c r="C215" t="n">
         <v>241.3099975585938</v>
@@ -6178,7 +6178,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>234.1179351806641</v>
+        <v>234.1179504394531</v>
       </c>
       <c r="C216" t="n">
         <v>246.9700012207031</v>
@@ -6207,7 +6207,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>246.1570587158203</v>
+        <v>246.1570434570312</v>
       </c>
       <c r="C217" t="n">
         <v>259.6700134277344</v>
@@ -6352,7 +6352,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>287.0843811035156</v>
+        <v>287.0842895507812</v>
       </c>
       <c r="C222" t="n">
         <v>299.7699890136719</v>
@@ -6381,7 +6381,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>277.8619384765625</v>
+        <v>277.8619079589844</v>
       </c>
       <c r="C223" t="n">
         <v>290.1400146484375</v>
@@ -6410,7 +6410,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>287.5022888183594</v>
+        <v>287.5023193359375</v>
       </c>
       <c r="C224" t="n">
         <v>298.7099914550781</v>
@@ -6439,7 +6439,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>288.1278686523438</v>
+        <v>288.1278991699219</v>
       </c>
       <c r="C225" t="n">
         <v>299.3599853515625</v>
@@ -6468,7 +6468,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>290.8613891601562</v>
+        <v>290.861328125</v>
       </c>
       <c r="C226" t="n">
         <v>302.2000122070312</v>
@@ -6497,7 +6497,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>282.0213928222656</v>
+        <v>282.0213623046875</v>
       </c>
       <c r="C227" t="n">
         <v>291.6099853515625</v>
@@ -6526,7 +6526,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>274.6712646484375</v>
+        <v>274.6712951660156</v>
       </c>
       <c r="C228" t="n">
         <v>284.010009765625</v>
@@ -6555,7 +6555,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>254.8259887695312</v>
+        <v>254.8260192871094</v>
       </c>
       <c r="C229" t="n">
         <v>263.489990234375</v>
@@ -6584,7 +6584,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>249.8498382568359</v>
+        <v>249.849853515625</v>
       </c>
       <c r="C230" t="n">
         <v>256.9800109863281</v>
@@ -6671,7 +6671,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>266.0378723144531</v>
+        <v>266.037841796875</v>
       </c>
       <c r="C233" t="n">
         <v>272.1199951171875</v>
